--- a/config/union/union_task.xlsx
+++ b/config/union/union_task.xlsx
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>金貨を200000消費</t>
+          <t>消耗200000金币</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>訓練センターで3回加速を行う</t>
+          <t>在训练中心进行3次加速</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>ギルドに5回寄付する</t>
+          <t>向公会捐赠5次</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ギルドダンジョンに累計12回挑戦</t>
+          <t>累计挑战12次公会地牢</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>スタミナを累計1500消費</t>
+          <t>累计消耗1500点体力</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>貢献度を累計7500獲得</t>
+          <t>累计贡献7500</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>ダイヤを累計50000消費</t>
+          <t>累计消费50000颗钻石</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>ギルドダンジョンに累計200回挑戦</t>
+          <t>累计挑战200次公会地下城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>祈願センターで欠片を累計10回贈る</t>
+          <t>祈愿中心累计赠送碎片10次</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
